--- a/बजेट माग estimate/thekka/माथिल्लो रिमाल घडेरी सिँचाई/माथिल्लो रिमाल घडेरी सिँचाई - sir.xlsx
+++ b/बजेट माग estimate/thekka/माथिल्लो रिमाल घडेरी सिँचाई/माथिल्लो रिमाल घडेरी सिँचाई - sir.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F834C5-13A2-4A1E-AA04-2A89382E2EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE6D48A-92EE-45CB-A761-CAD158A6FF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -117,24 +117,9 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Budget allocated</t>
-  </si>
-  <si>
-    <t>Municipal payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingencies </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maintanince </t>
-  </si>
-  <si>
     <t>F.Y.: 2082/2083</t>
   </si>
   <si>
-    <t>User contribution</t>
-  </si>
-  <si>
     <t>Length (m)</t>
   </si>
   <si>
@@ -147,27 +132,15 @@
     <t>PS</t>
   </si>
   <si>
-    <t>-13% VAT for sand</t>
-  </si>
-  <si>
     <t>Plain cement concrete (1:2:4)</t>
   </si>
   <si>
-    <t>-13% VAT for cement</t>
-  </si>
-  <si>
-    <t>-13% VAT for aggregate</t>
-  </si>
-  <si>
     <t>sqm</t>
   </si>
   <si>
     <t>length</t>
   </si>
   <si>
-    <t>-13% VAT for block stone</t>
-  </si>
-  <si>
     <t>thickness</t>
   </si>
   <si>
@@ -180,9 +153,6 @@
     <t>Total Weight (Kg)</t>
   </si>
   <si>
-    <t>-13% VAT for nails</t>
-  </si>
-  <si>
     <t>Earthwork in Excavation in ordinary soil</t>
   </si>
   <si>
@@ -195,16 +165,7 @@
     <t>Kg</t>
   </si>
   <si>
-    <t>-13% VAT for MS bars</t>
-  </si>
-  <si>
-    <t>-13% VAT for Bind wire</t>
-  </si>
-  <si>
     <t>Form work for concrete work</t>
-  </si>
-  <si>
-    <t>-13% VAT for local wood</t>
   </si>
   <si>
     <t>breadth</t>
@@ -415,7 +376,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -529,21 +490,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -565,6 +511,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1092,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -1107,113 +1059,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
     </row>
     <row r="2" spans="1:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
     </row>
     <row r="5" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
+      <c r="A6" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
+      <c r="H6" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="A7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
+      <c r="H7" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -1256,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="14"/>
@@ -1272,7 +1224,7 @@
     <row r="10" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C10" s="18">
         <v>0.5</v>
@@ -1298,7 +1250,7 @@
     <row r="11" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C11" s="18">
         <v>0.5</v>
@@ -1312,7 +1264,7 @@
         <v>1.5239256324291375</v>
       </c>
       <c r="F11" s="7">
-        <f>F34</f>
+        <f>F30</f>
         <v>3.047851264858275</v>
       </c>
       <c r="G11" s="7">
@@ -1327,7 +1279,7 @@
     <row r="12" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C12" s="18">
         <v>0.5</v>
@@ -1340,7 +1292,7 @@
         <v>0.45</v>
       </c>
       <c r="F12" s="7">
-        <f>F35</f>
+        <f>F31</f>
         <v>1.2</v>
       </c>
       <c r="G12" s="7">
@@ -1366,14 +1318,15 @@
         <v>23.007449104850526</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I13" s="2">
-        <v>963.05</v>
+        <f>1.15*963.05</f>
+        <v>1107.5074999999999</v>
       </c>
       <c r="J13" s="25">
         <f>G13*I13</f>
-        <v>22157.323860426299</v>
+        <v>25480.922439490241</v>
       </c>
       <c r="K13" s="23"/>
     </row>
@@ -1395,7 +1348,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -1410,15 +1363,15 @@
     <row r="16" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="str">
-        <f>B10</f>
+        <f t="shared" ref="B16:D18" si="0">B10</f>
         <v>-for kulo</v>
       </c>
       <c r="C16" s="18">
-        <f>C10</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="D16" s="7">
-        <f>D10</f>
+        <f t="shared" si="0"/>
         <v>30.48</v>
       </c>
       <c r="E16" s="7">
@@ -1439,15 +1392,15 @@
     <row r="17" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="str">
-        <f>B11</f>
+        <f t="shared" si="0"/>
         <v>-for masonary wall 1</v>
       </c>
       <c r="C17" s="18">
-        <f>C11</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="D17" s="7">
-        <f>D11</f>
+        <f t="shared" si="0"/>
         <v>7.0100579091740318</v>
       </c>
       <c r="E17" s="7">
@@ -1470,15 +1423,15 @@
     <row r="18" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="str">
-        <f>B12</f>
+        <f t="shared" si="0"/>
         <v>-for masonary wall 2</v>
       </c>
       <c r="C18" s="18">
-        <f>C12</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="D18" s="7">
-        <f>D12</f>
+        <f t="shared" si="0"/>
         <v>3.9622066443157573</v>
       </c>
       <c r="E18" s="7">
@@ -1512,23 +1465,21 @@
         <v>18.606899104850527</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I19" s="2">
-        <f>4493.69</f>
-        <v>4493.6899999999996</v>
+        <f>1.15*4493.69</f>
+        <v>5167.7434999999996</v>
       </c>
       <c r="J19" s="25">
         <f>G19*I19</f>
-        <v>83613.636438475762</v>
+        <v>96155.681904247118</v>
       </c>
       <c r="K19" s="23"/>
     </row>
     <row r="20" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
-      <c r="B20" s="17" t="s">
-        <v>37</v>
-      </c>
+      <c r="B20" s="19"/>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
@@ -1536,15 +1487,16 @@
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="25">
-        <f>0.13*G19*3091.19</f>
-        <v>7477.2698577099773</v>
-      </c>
+      <c r="J20" s="19"/>
       <c r="K20" s="19"/>
     </row>
     <row r="21" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="16">
+        <v>3</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>26</v>
+      </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
@@ -1556,17 +1508,28 @@
       <c r="K21" s="19"/>
     </row>
     <row r="22" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>3</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="17" t="str">
+        <f>B16</f>
+        <v>-for kulo</v>
+      </c>
+      <c r="C22" s="18">
+        <f>C16</f>
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="7">
+        <v>30.48</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="F22" s="19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G22" s="7">
+        <f>PRODUCT(C22:F22)</f>
+        <v>0.62864999999999993</v>
+      </c>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
       <c r="J22" s="19"/>
@@ -1575,25 +1538,28 @@
     <row r="23" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="17" t="str">
-        <f>B16</f>
-        <v>-for kulo</v>
+        <f>B17</f>
+        <v>-for masonary wall 1</v>
       </c>
       <c r="C23" s="18">
-        <f>C16</f>
-        <v>0.5</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="D23" s="7">
-        <v>30.48</v>
+        <f>D30</f>
+        <v>7.0100579091740318</v>
       </c>
       <c r="E23" s="7">
-        <v>0.54999999999999993</v>
+        <f>F30/2</f>
+        <v>1.5239256324291375</v>
       </c>
       <c r="F23" s="19">
-        <v>7.4999999999999997E-2</v>
+        <f>0.05</f>
+        <v>0.05</v>
       </c>
       <c r="G23" s="7">
         <f>PRODUCT(C23:F23)</f>
-        <v>0.62864999999999993</v>
+        <v>0.53414034663014565</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
@@ -1602,29 +1568,23 @@
     </row>
     <row r="24" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
-      <c r="B24" s="17" t="str">
-        <f>B17</f>
-        <v>-for masonary wall 1</v>
-      </c>
+      <c r="B24" s="17"/>
       <c r="C24" s="18">
-        <f>1</f>
         <v>1</v>
       </c>
       <c r="D24" s="7">
-        <f>D34</f>
+        <f>D23</f>
         <v>7.0100579091740318</v>
       </c>
-      <c r="E24" s="7">
-        <f>F34/2</f>
-        <v>1.5239256324291375</v>
+      <c r="E24" s="5">
+        <v>0.45</v>
       </c>
       <c r="F24" s="19">
-        <f>0.05</f>
         <v>0.05</v>
       </c>
       <c r="G24" s="7">
         <f>PRODUCT(C24:F24)</f>
-        <v>0.53414034663014565</v>
+        <v>0.15772630295641574</v>
       </c>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
@@ -1633,15 +1593,18 @@
     </row>
     <row r="25" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
+      <c r="B25" s="17" t="str">
+        <f>B18</f>
+        <v>-for masonary wall 2</v>
+      </c>
       <c r="C25" s="18">
         <v>1</v>
       </c>
       <c r="D25" s="7">
-        <f>D24</f>
-        <v>7.0100579091740318</v>
-      </c>
-      <c r="E25" s="5">
+        <f>D31</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E25" s="7">
         <v>0.45</v>
       </c>
       <c r="F25" s="19">
@@ -1649,7 +1612,7 @@
       </c>
       <c r="G25" s="7">
         <f>PRODUCT(C25:F25)</f>
-        <v>0.15772630295641574</v>
+        <v>8.9149649497104549E-2</v>
       </c>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
@@ -1658,15 +1621,12 @@
     </row>
     <row r="26" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
-      <c r="B26" s="17" t="str">
-        <f>B18</f>
-        <v>-for masonary wall 2</v>
-      </c>
+      <c r="B26" s="17"/>
       <c r="C26" s="18">
         <v>1</v>
       </c>
       <c r="D26" s="7">
-        <f>D35</f>
+        <f>D31</f>
         <v>3.9622066443157573</v>
       </c>
       <c r="E26" s="7">
@@ -1684,60 +1644,51 @@
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
     </row>
-    <row r="27" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7">
-        <f>D35</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="F27" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="G27" s="7">
-        <f>PRODUCT(C27:F27)</f>
-        <v>8.9149649497104549E-2</v>
-      </c>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-    </row>
-    <row r="28" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
-      <c r="B28" s="21" t="s">
+    <row r="27" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="2">
-        <f>SUM(G23:G27)</f>
+      <c r="C27" s="22"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="2">
+        <f>SUM(G22:G26)</f>
         <v>1.4988159485807704</v>
       </c>
-      <c r="H28" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="2">
-        <v>13343.7</v>
-      </c>
-      <c r="J28" s="25">
-        <f>G28*I28</f>
-        <v>19999.750373077226</v>
-      </c>
-      <c r="K28" s="23"/>
-    </row>
-    <row r="29" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17" t="s">
-        <v>31</v>
+      <c r="H27" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="2">
+        <f>1.15*13343.7</f>
+        <v>15345.254999999999</v>
+      </c>
+      <c r="J27" s="25">
+        <f>G27*I27</f>
+        <v>22999.712929038807</v>
+      </c>
+      <c r="K27" s="23"/>
+    </row>
+    <row r="28" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+    </row>
+    <row r="29" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="16">
+        <v>4</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -1746,68 +1697,99 @@
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="25">
-        <f>0.13*G28*1413.27</f>
-        <v>275.37011003459691</v>
-      </c>
+      <c r="J29" s="19"/>
       <c r="K29" s="19"/>
     </row>
     <row r="30" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
-      <c r="B30" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+      <c r="B30" s="17" t="str">
+        <f t="shared" ref="B30:D31" si="1">B11</f>
+        <v>-for masonary wall 1</v>
+      </c>
+      <c r="C30" s="18">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" si="1"/>
+        <v>7.0100579091740318</v>
+      </c>
+      <c r="E30" s="7">
+        <f>((F30/2)+0.45)/2</f>
+        <v>0.98696281621456872</v>
+      </c>
+      <c r="F30" s="7">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="G30" s="7">
+        <f>PRODUCT(C30:F30)</f>
+        <v>10.543533215278289</v>
+      </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
-      <c r="J30" s="25">
-        <f>0.13*G28*4096</f>
-        <v>798.08951630028866</v>
-      </c>
+      <c r="J30" s="19"/>
       <c r="K30" s="19"/>
     </row>
     <row r="31" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
-      <c r="B31" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
+      <c r="B31" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v>-for masonary wall 2</v>
+      </c>
+      <c r="C31" s="18">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="7">
+        <f t="shared" si="1"/>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="F31" s="7">
+        <f>1.2</f>
+        <v>1.2</v>
+      </c>
+      <c r="G31" s="7">
+        <f>PRODUCT(C31:F31)</f>
+        <v>1.0697957939652545</v>
+      </c>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
-      <c r="J31" s="25">
-        <f>0.13*G28*(368.76+737.51+1743.21)</f>
-        <v>555.20998899105143</v>
-      </c>
+      <c r="J31" s="19"/>
       <c r="K31" s="19"/>
     </row>
-    <row r="32" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-    </row>
-    <row r="33" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>4</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>54</v>
-      </c>
+    <row r="32" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="2">
+        <f>SUM(G30:G31)</f>
+        <v>11.613329009243543</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="2">
+        <f>1.15*12225.55</f>
+        <v>14059.382499999998</v>
+      </c>
+      <c r="J32" s="25">
+        <f>G32*I32</f>
+        <v>163276.23463930099</v>
+      </c>
+      <c r="K32" s="23"/>
+    </row>
+    <row r="33" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="19"/>
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
@@ -1818,68 +1800,52 @@
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
     </row>
-    <row r="34" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="17" t="str">
-        <f>B11</f>
-        <v>-for masonary wall 1</v>
-      </c>
-      <c r="C34" s="18">
-        <f>C11</f>
-        <v>0.5</v>
-      </c>
-      <c r="D34" s="7">
-        <f>D11</f>
-        <v>7.0100579091740318</v>
-      </c>
-      <c r="E34" s="7">
-        <f>((F34/2)+0.45)/2</f>
-        <v>0.98696281621456872</v>
-      </c>
-      <c r="F34" s="7">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="G34" s="7">
-        <f>PRODUCT(C34:F34)</f>
-        <v>10.543533215278289</v>
-      </c>
+    <row r="34" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>5</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
     </row>
-    <row r="35" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="17" t="str">
-        <f>B12</f>
-        <v>-for masonary wall 2</v>
-      </c>
-      <c r="C35" s="18">
-        <f>C12</f>
-        <v>0.5</v>
+        <f>B40</f>
+        <v>-for kulo shear wall</v>
+      </c>
+      <c r="C35" s="19">
+        <f>C40*2</f>
+        <v>4</v>
       </c>
       <c r="D35" s="7">
-        <f>D12</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.45</v>
-      </c>
+        <f>D40</f>
+        <v>30.48</v>
+      </c>
+      <c r="E35" s="7"/>
       <c r="F35" s="7">
-        <f>1.2</f>
-        <v>1.2</v>
+        <f>F40</f>
+        <v>0.35</v>
       </c>
       <c r="G35" s="7">
         <f>PRODUCT(C35:F35)</f>
-        <v>1.0697957939652545</v>
+        <v>42.671999999999997</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
     </row>
-    <row r="36" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20"/>
       <c r="B36" s="21" t="s">
         <v>16</v>
@@ -1889,26 +1855,25 @@
       <c r="E36" s="23"/>
       <c r="F36" s="23"/>
       <c r="G36" s="2">
-        <f>SUM(G34:G35)</f>
-        <v>11.613329009243543</v>
+        <f>SUM(G35:G35)</f>
+        <v>42.671999999999997</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I36" s="2">
-        <v>12225.55</v>
+        <f>1.15*11188.35/10</f>
+        <v>1286.6602499999999</v>
       </c>
       <c r="J36" s="25">
         <f>G36*I36</f>
-        <v>141979.33446895739</v>
+        <v>54904.366187999993</v>
       </c>
       <c r="K36" s="23"/>
     </row>
-    <row r="37" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
-      <c r="B37" s="17" t="s">
-        <v>31</v>
-      </c>
+      <c r="B37" s="19"/>
       <c r="C37" s="19"/>
       <c r="D37" s="19"/>
       <c r="E37" s="19"/>
@@ -1916,16 +1881,15 @@
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
-      <c r="J37" s="25">
-        <f>0.13*G36*1492.66</f>
-        <v>2253.5177182618709</v>
-      </c>
+      <c r="J37" s="19"/>
       <c r="K37" s="19"/>
     </row>
-    <row r="38" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
-      <c r="B38" s="17" t="s">
-        <v>33</v>
+    <row r="38" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>6</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>34</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="19"/>
@@ -1934,170 +1898,216 @@
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
-      <c r="J38" s="25">
-        <f>0.13*G36*1356.8</f>
-        <v>2048.4054239664129</v>
-      </c>
+      <c r="J38" s="19"/>
       <c r="K38" s="19"/>
     </row>
-    <row r="39" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
+        <v>44</v>
+      </c>
+      <c r="C39" s="18">
+        <f>C22</f>
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="7">
+        <f>D22</f>
+        <v>30.48</v>
+      </c>
+      <c r="E39" s="7">
+        <f>E22</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="G39" s="7">
+        <f>PRODUCT(C39:F39)</f>
+        <v>0.83820000000000006</v>
+      </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="25">
-        <f>0.13*G36*2833.59</f>
-        <v>4277.9636831493135</v>
-      </c>
+      <c r="J39" s="19"/>
       <c r="K39" s="19"/>
     </row>
-    <row r="40" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
+      <c r="B40" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="18">
+        <v>2</v>
+      </c>
+      <c r="D40" s="7">
+        <v>30.48</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="F40" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="G40" s="7">
+        <f>PRODUCT(C40:F40)</f>
+        <v>2.1335999999999999</v>
+      </c>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
     </row>
-    <row r="41" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
-        <v>5</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-    </row>
-    <row r="42" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="2">
+        <f>SUM(G39:G40)</f>
+        <v>2.9718</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="2">
+        <f>1.15*14337.7</f>
+        <v>16488.355</v>
+      </c>
+      <c r="J41" s="25">
+        <f>G41*I41</f>
+        <v>49000.093389000001</v>
+      </c>
+      <c r="K41" s="23"/>
+    </row>
+    <row r="42" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
-      <c r="B42" s="17" t="str">
-        <f>B49</f>
-        <v>-for kulo shear wall</v>
-      </c>
-      <c r="C42" s="19">
-        <f>C49*2</f>
-        <v>4</v>
-      </c>
-      <c r="D42" s="7">
-        <f>D49</f>
-        <v>30.48</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7">
-        <f>F49</f>
-        <v>0.35</v>
-      </c>
-      <c r="G42" s="7">
-        <f>PRODUCT(C42:F42)</f>
-        <v>42.671999999999997</v>
-      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
       <c r="H42" s="19"/>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
-    <row r="43" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20"/>
-      <c r="B43" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="2">
-        <f>SUM(G42:G42)</f>
-        <v>42.671999999999997</v>
-      </c>
-      <c r="H43" s="24" t="s">
+    <row r="43" spans="1:17" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <v>7</v>
+      </c>
+      <c r="B43" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="I43" s="2">
-        <f>11188.35/10</f>
-        <v>1118.835</v>
-      </c>
-      <c r="J43" s="25">
-        <f>G43*I43</f>
-        <v>47742.92712</v>
-      </c>
-      <c r="K43" s="23"/>
-    </row>
-    <row r="44" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+    </row>
+    <row r="44" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
-      <c r="B44" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
+      <c r="B44" s="17" t="str">
+        <f>B22</f>
+        <v>-for kulo</v>
+      </c>
+      <c r="C44" s="19">
+        <f>TRUNC((Sheet1!B10-0.1)/0.15,0)+1</f>
+        <v>203</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F44" s="7">
+        <f>PRODUCT(C44:E44)</f>
+        <v>144.10493827160494</v>
+      </c>
+      <c r="G44" s="7">
+        <f>F44</f>
+        <v>144.10493827160494</v>
+      </c>
       <c r="H44" s="19"/>
       <c r="I44" s="19"/>
-      <c r="J44" s="25">
-        <f>0.13*G43*6314/10</f>
-        <v>3502.6031039999993</v>
-      </c>
+      <c r="J44" s="19"/>
       <c r="K44" s="19"/>
     </row>
-    <row r="45" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C45" s="19">
+        <f>(TRUNC((Sheet1!C10-Sheet1!E10)/0.15,0)+1)+2*(TRUNC((Sheet1!D10/0.15),0)+1)</f>
+        <v>10</v>
+      </c>
+      <c r="D45" s="7">
+        <v>30.38</v>
+      </c>
+      <c r="E45" s="7">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F45" s="7">
+        <f>PRODUCT(C45:E45)</f>
+        <v>187.53086419753086</v>
+      </c>
+      <c r="G45" s="7">
+        <f>F45</f>
+        <v>187.53086419753086</v>
+      </c>
       <c r="H45" s="19"/>
       <c r="I45" s="19"/>
-      <c r="J45" s="25">
-        <f>0.13*G43*330/10</f>
-        <v>183.06287999999998</v>
-      </c>
+      <c r="J45" s="19"/>
       <c r="K45" s="19"/>
     </row>
-    <row r="46" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="16">
-        <v>6</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>44</v>
-      </c>
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="20"/>
+      <c r="B46" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="22"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="2">
+        <f>SUM(G44:G45)</f>
+        <v>331.6358024691358</v>
+      </c>
+      <c r="H46" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="2">
+        <f>1.15*9831.6/100</f>
+        <v>113.0634</v>
+      </c>
+      <c r="J46" s="25">
+        <f>G46*I46</f>
+        <v>37495.871388888889</v>
+      </c>
+      <c r="K46" s="23"/>
+    </row>
+    <row r="47" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="19"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
       <c r="E47" s="19"/>
@@ -2108,506 +2118,134 @@
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
     </row>
-    <row r="48" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16"/>
-      <c r="B48" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="18">
-        <f>C23</f>
-        <v>0.5</v>
-      </c>
-      <c r="D48" s="7">
-        <f>D23</f>
-        <v>30.48</v>
-      </c>
-      <c r="E48" s="7">
-        <f>E23</f>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="F48" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="G48" s="7">
+    <row r="48" spans="1:17" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="20">
+        <v>8</v>
+      </c>
+      <c r="B48" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" s="22">
+        <v>1</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="43">
         <f>PRODUCT(C48:F48)</f>
-        <v>0.83820000000000006</v>
-      </c>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J48" s="43">
+        <f>G48*I48</f>
+        <v>5000</v>
+      </c>
+      <c r="K48" s="23"/>
+      <c r="Q48" s="5"/>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
-      <c r="B49" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="18">
-        <v>2</v>
-      </c>
-      <c r="D49" s="7">
-        <v>30.48</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="F49" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="G49" s="7">
-        <f>PRODUCT(C49:F49)</f>
-        <v>2.1335999999999999</v>
-      </c>
+      <c r="B49" s="40"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="20"/>
-      <c r="B50" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="22"/>
+      <c r="A50" s="20">
+        <v>9</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="22">
+        <v>1</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="23"/>
       <c r="F50" s="23"/>
-      <c r="G50" s="2">
-        <f>SUM(G48:G49)</f>
-        <v>2.9718</v>
+      <c r="G50" s="24">
+        <f>PRODUCT(C50:F50)</f>
+        <v>1</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I50" s="2">
-        <v>14337.7</v>
-      </c>
-      <c r="J50" s="25">
+        <v>500</v>
+      </c>
+      <c r="J50" s="24">
         <f>G50*I50</f>
-        <v>42608.776860000005</v>
+        <v>500</v>
       </c>
       <c r="K50" s="23"/>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="25">
-        <f>0.13*G50*5120</f>
-        <v>1978.03008</v>
-      </c>
-      <c r="K51" s="19"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="23"/>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="16"/>
-      <c r="B52" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="30"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
       <c r="J52" s="25">
-        <f>0.13*G50*1349.75</f>
-        <v>521.4543165</v>
-      </c>
-      <c r="K52" s="19"/>
+        <f>SUM(J10:J50)</f>
+        <v>454812.88287796604</v>
+      </c>
+      <c r="K52" s="32"/>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="25">
-        <f>0.13*G50*(972.17+1910.82)</f>
-        <v>1113.7970586599999</v>
-      </c>
-      <c r="K53" s="19"/>
-    </row>
-    <row r="54" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="16"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="19"/>
-    </row>
-    <row r="55" spans="1:17" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A55" s="16">
-        <v>7</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E55" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="F55" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-    </row>
-    <row r="56" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="16"/>
-      <c r="B56" s="17" t="str">
-        <f>B23</f>
-        <v>-for kulo</v>
-      </c>
-      <c r="C56" s="19">
-        <f>TRUNC((Sheet1!B10-0.1)/0.15,0)+1</f>
-        <v>203</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="E56" s="7">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="F56" s="7">
-        <f>PRODUCT(C56:E56)</f>
-        <v>144.10493827160494</v>
-      </c>
-      <c r="G56" s="7">
-        <f>F56</f>
-        <v>144.10493827160494</v>
-      </c>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="19"/>
-    </row>
-    <row r="57" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16"/>
-      <c r="B57" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57" s="19">
-        <f>(TRUNC((Sheet1!C10-Sheet1!E10)/0.15,0)+1)+2*(TRUNC((Sheet1!D10/0.15),0)+1)</f>
-        <v>10</v>
-      </c>
-      <c r="D57" s="7">
-        <v>30.38</v>
-      </c>
-      <c r="E57" s="7">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
-      </c>
-      <c r="F57" s="7">
-        <f>PRODUCT(C57:E57)</f>
-        <v>187.53086419753086</v>
-      </c>
-      <c r="G57" s="7">
-        <f>F57</f>
-        <v>187.53086419753086</v>
-      </c>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-    </row>
-    <row r="58" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20"/>
-      <c r="B58" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="22"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="2">
-        <f>SUM(G56:G57)</f>
-        <v>331.6358024691358</v>
-      </c>
-      <c r="H58" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" s="2">
-        <f>9831.6/100</f>
-        <v>98.316000000000003</v>
-      </c>
-      <c r="J58" s="25">
-        <f>G58*I58</f>
-        <v>32605.105555555554</v>
-      </c>
-      <c r="K58" s="23"/>
-    </row>
-    <row r="59" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="16"/>
-      <c r="B59" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="25">
-        <f>0.13*G58*9450/100</f>
-        <v>4074.145833333333</v>
-      </c>
-      <c r="K59" s="19"/>
-    </row>
-    <row r="60" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="16"/>
-      <c r="B60" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="25">
-        <f>0.13*G58*120/100</f>
-        <v>51.735185185185181</v>
-      </c>
-      <c r="K60" s="19"/>
-    </row>
-    <row r="61" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="16"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
-    </row>
-    <row r="62" spans="1:17" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="20">
-        <v>8</v>
-      </c>
-      <c r="B62" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="22">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="43">
-        <f>PRODUCT(C62:F62)</f>
-        <v>1</v>
-      </c>
-      <c r="H62" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J62" s="43">
-        <f>G62*I62</f>
-        <v>5000</v>
-      </c>
-      <c r="K62" s="23"/>
-      <c r="Q62" s="5"/>
-    </row>
-    <row r="63" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="16"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="19"/>
-    </row>
-    <row r="64" spans="1:17" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20">
-        <v>9</v>
-      </c>
-      <c r="B64" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="22">
-        <v>1</v>
-      </c>
-      <c r="D64" s="1"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="24">
-        <f>PRODUCT(C64:F64)</f>
-        <v>1</v>
-      </c>
-      <c r="H64" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="I64" s="2">
-        <v>500</v>
-      </c>
-      <c r="J64" s="24">
-        <f>G64*I64</f>
-        <v>500</v>
-      </c>
-      <c r="K64" s="23"/>
-    </row>
-    <row r="65" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="20"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="24"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="25"/>
-      <c r="K65" s="23"/>
-    </row>
-    <row r="66" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="28"/>
-      <c r="B66" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="30"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25">
-        <f>SUM(J10:J64)</f>
-        <v>425317.50943258416</v>
-      </c>
-      <c r="K66" s="32"/>
-    </row>
-    <row r="67" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="Q67" s="6"/>
-    </row>
-    <row r="68" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="33"/>
-      <c r="B68" s="34" t="s">
+      <c r="Q53" s="6"/>
+    </row>
+    <row r="54" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="33"/>
+      <c r="B54" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C68" s="45">
-        <f>J66</f>
-        <v>425317.50943258416</v>
-      </c>
-      <c r="D68" s="46"/>
-      <c r="E68" s="35">
-        <v>100</v>
-      </c>
-      <c r="F68" s="33"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="39"/>
-      <c r="Q68" s="5"/>
-    </row>
-    <row r="69" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" s="47">
-        <v>375000</v>
-      </c>
-      <c r="D69" s="48"/>
-      <c r="E69" s="35"/>
-    </row>
-    <row r="70" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C70" s="47">
-        <f>C69-C72-C73</f>
-        <v>356250</v>
-      </c>
-      <c r="D70" s="48"/>
-      <c r="E70" s="35">
-        <f>C70/C68*100</f>
-        <v>83.76095319359716</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C71" s="49">
-        <f>C68-C70</f>
-        <v>69067.509432584164</v>
-      </c>
-      <c r="D71" s="49"/>
-      <c r="E71" s="35">
-        <f>100-E70</f>
-        <v>16.23904680640284</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="45">
-        <f>C69*0.03</f>
-        <v>11250</v>
-      </c>
-      <c r="D72" s="46"/>
-      <c r="E72" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="45">
-        <f>C69*0.02</f>
-        <v>7500</v>
-      </c>
-      <c r="D73" s="46"/>
-      <c r="E73" s="35">
-        <v>2</v>
-      </c>
-      <c r="Q73"/>
+      <c r="C54" s="53">
+        <f>J52</f>
+        <v>454812.88287796604</v>
+      </c>
+      <c r="D54" s="54"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="33"/>
+      <c r="I54" s="37"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="39"/>
+      <c r="Q54" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="10">
+    <mergeCell ref="C54:D54"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -2617,12 +2255,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2639,7 +2271,7 @@
   <sheetData>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -2647,16 +2279,16 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
